--- a/excel_template/Multipl_Mastersheet_Template.xlsx
+++ b/excel_template/Multipl_Mastersheet_Template.xlsx
@@ -19,10 +19,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="#,##0;(#,##0);&quot;-&quot;"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="165" formatCode="#,##0.0"/>
   </numFmts>
   <fonts count="10">
     <font>
@@ -123,7 +122,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -160,10 +159,13 @@
     <xf numFmtId="4" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -734,160 +736,160 @@
         </is>
       </c>
       <c r="B1" s="13" t="n">
-        <v>44621</v>
+        <v>44621.5</v>
       </c>
       <c r="C1" s="13" t="n">
-        <v>44652</v>
+        <v>44652.5</v>
       </c>
       <c r="D1" s="13" t="n">
-        <v>44682</v>
+        <v>44682.5</v>
       </c>
       <c r="E1" s="13" t="n">
-        <v>44713</v>
+        <v>44713.5</v>
       </c>
       <c r="F1" s="13" t="n">
-        <v>44743</v>
+        <v>44743.5</v>
       </c>
       <c r="G1" s="13" t="n">
-        <v>44774</v>
+        <v>44774.5</v>
       </c>
       <c r="H1" s="13" t="n">
-        <v>44805</v>
+        <v>44805.5</v>
       </c>
       <c r="I1" s="13" t="n">
-        <v>44835</v>
+        <v>44835.5</v>
       </c>
       <c r="J1" s="13" t="n">
-        <v>44866</v>
+        <v>44866.5</v>
       </c>
       <c r="K1" s="13" t="n">
-        <v>44896</v>
+        <v>44896.5</v>
       </c>
       <c r="L1" s="13" t="n">
-        <v>44927</v>
+        <v>44927.5</v>
       </c>
       <c r="M1" s="13" t="n">
-        <v>44958</v>
+        <v>44958.5</v>
       </c>
       <c r="N1" s="13" t="n">
-        <v>44986</v>
+        <v>44986.5</v>
       </c>
       <c r="O1" s="13" t="n">
-        <v>45017</v>
+        <v>45017.5</v>
       </c>
       <c r="P1" s="13" t="n">
-        <v>45047</v>
+        <v>45047.5</v>
       </c>
       <c r="Q1" s="13" t="n">
-        <v>45078</v>
+        <v>45078.5</v>
       </c>
       <c r="R1" s="13" t="n">
-        <v>45108</v>
+        <v>45108.5</v>
       </c>
       <c r="S1" s="13" t="n">
-        <v>45139</v>
+        <v>45139.5</v>
       </c>
       <c r="T1" s="13" t="n">
-        <v>45170</v>
+        <v>45170.5</v>
       </c>
       <c r="U1" s="13" t="n">
-        <v>45200</v>
+        <v>45200.5</v>
       </c>
       <c r="V1" s="13" t="n">
-        <v>45231</v>
+        <v>45231.5</v>
       </c>
       <c r="W1" s="13" t="n">
-        <v>45261</v>
+        <v>45261.5</v>
       </c>
       <c r="X1" s="13" t="n">
-        <v>45292</v>
+        <v>45292.5</v>
       </c>
       <c r="Y1" s="13" t="n">
-        <v>45323</v>
+        <v>45323.5</v>
       </c>
       <c r="Z1" s="13" t="n">
-        <v>45352</v>
+        <v>45352.5</v>
       </c>
       <c r="AA1" s="13" t="n">
-        <v>45383</v>
+        <v>45383.5</v>
       </c>
       <c r="AB1" s="13" t="n">
-        <v>45413</v>
+        <v>45413.5</v>
       </c>
       <c r="AC1" s="13" t="n">
-        <v>45444</v>
+        <v>45444.5</v>
       </c>
       <c r="AD1" s="13" t="n">
-        <v>45474</v>
+        <v>45474.5</v>
       </c>
       <c r="AE1" s="13" t="n">
-        <v>45505</v>
+        <v>45505.5</v>
       </c>
       <c r="AF1" s="13" t="n">
-        <v>45536</v>
+        <v>45536.5</v>
       </c>
       <c r="AG1" s="13" t="n">
-        <v>45566</v>
+        <v>45566.5</v>
       </c>
       <c r="AH1" s="13" t="n">
-        <v>45597</v>
+        <v>45597.5</v>
       </c>
       <c r="AI1" s="13" t="n">
-        <v>45627</v>
+        <v>45627.5</v>
       </c>
       <c r="AJ1" s="13" t="n">
-        <v>45658</v>
+        <v>45658.5</v>
       </c>
       <c r="AK1" s="13" t="n">
-        <v>45689</v>
+        <v>45689.5</v>
       </c>
       <c r="AL1" s="13" t="n">
-        <v>45717</v>
+        <v>45717.5</v>
       </c>
       <c r="AM1" s="13" t="n">
-        <v>45748</v>
+        <v>45748.5</v>
       </c>
       <c r="AN1" s="13" t="n">
-        <v>45778</v>
+        <v>45778.5</v>
       </c>
       <c r="AO1" s="13" t="n">
-        <v>45809</v>
+        <v>45809.5</v>
       </c>
       <c r="AP1" s="13" t="n">
-        <v>45839</v>
+        <v>45839.5</v>
       </c>
       <c r="AQ1" s="13" t="n">
-        <v>45870</v>
+        <v>45870.5</v>
       </c>
       <c r="AR1" s="13" t="n">
-        <v>45930</v>
+        <v>45901.5</v>
       </c>
       <c r="AS1" s="13" t="n">
-        <v>45961</v>
+        <v>45931.5</v>
       </c>
       <c r="AT1" s="13" t="n">
-        <v>45962</v>
+        <v>45962.5</v>
       </c>
       <c r="AU1" s="13" t="n">
-        <v>45992</v>
+        <v>45992.5</v>
       </c>
       <c r="AV1" s="13" t="n">
-        <v>46023</v>
+        <v>46023.5</v>
       </c>
       <c r="AW1" s="13" t="n">
-        <v>46054</v>
+        <v>46054.5</v>
       </c>
       <c r="AX1" s="13" t="n">
-        <v>46082</v>
+        <v>46082.5</v>
       </c>
       <c r="AY1" s="13" t="n">
-        <v>46113</v>
+        <v>46113.5</v>
       </c>
       <c r="AZ1" s="13" t="n">
-        <v>46143</v>
+        <v>46143.5</v>
       </c>
       <c r="BA1" s="13" t="n">
-        <v>46174</v>
+        <v>46174.5</v>
       </c>
     </row>
     <row r="2">
@@ -1711,160 +1713,160 @@
           <t>Assets Under Advice (AUA)</t>
         </is>
       </c>
-      <c r="B7" s="16" t="n">
+      <c r="B7" s="18" t="n">
         <v>15</v>
       </c>
-      <c r="C7" s="16" t="n">
+      <c r="C7" s="18" t="n">
         <v>15.29922875204067</v>
       </c>
-      <c r="D7" s="16" t="n">
+      <c r="D7" s="18" t="n">
         <v>16.1923741583098</v>
       </c>
-      <c r="E7" s="16" t="n">
+      <c r="E7" s="18" t="n">
         <v>16.31365678593782</v>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="18" t="n">
         <v>19.056878139</v>
       </c>
-      <c r="G7" s="16" t="n">
+      <c r="G7" s="18" t="n">
         <v>20.67105000034613</v>
       </c>
-      <c r="H7" s="16" t="n">
+      <c r="H7" s="18" t="n">
         <v>22.80923948860026</v>
       </c>
-      <c r="I7" s="16" t="n">
+      <c r="I7" s="18" t="n">
         <v>25.43263530958258</v>
       </c>
-      <c r="J7" s="16" t="n">
+      <c r="J7" s="18" t="n">
         <v>28.562235514</v>
       </c>
-      <c r="K7" s="16" t="n">
+      <c r="K7" s="18" t="n">
         <v>29.627741842</v>
       </c>
-      <c r="L7" s="16" t="n">
+      <c r="L7" s="18" t="n">
         <v>31.416548332</v>
       </c>
-      <c r="M7" s="16" t="n">
+      <c r="M7" s="18" t="n">
         <v>31.746063688</v>
       </c>
-      <c r="N7" s="16" t="n">
+      <c r="N7" s="18" t="n">
         <v>33.945827885</v>
       </c>
-      <c r="O7" s="16" t="n">
+      <c r="O7" s="18" t="n">
         <v>36.94784525</v>
       </c>
-      <c r="P7" s="16" t="n">
+      <c r="P7" s="18" t="n">
         <v>39.195087465</v>
       </c>
-      <c r="Q7" s="16" t="n">
+      <c r="Q7" s="18" t="n">
         <v>40.26721889499999</v>
       </c>
-      <c r="R7" s="16" t="n">
+      <c r="R7" s="18" t="n">
         <v>43.33598582099999</v>
       </c>
-      <c r="S7" s="16" t="n">
+      <c r="S7" s="18" t="n">
         <v>45.491807962</v>
       </c>
-      <c r="T7" s="16" t="n">
+      <c r="T7" s="18" t="n">
         <v>48.52882259699999</v>
       </c>
-      <c r="U7" s="16" t="n">
+      <c r="U7" s="18" t="n">
         <v>51.69233382300001</v>
       </c>
-      <c r="V7" s="16" t="n">
+      <c r="V7" s="18" t="n">
         <v>54.8750501</v>
       </c>
-      <c r="W7" s="16" t="n">
+      <c r="W7" s="18" t="n">
         <v>57.30358606499998</v>
       </c>
-      <c r="X7" s="16" t="n">
+      <c r="X7" s="18" t="n">
         <v>62.3747391</v>
       </c>
-      <c r="Y7" s="16" t="n">
+      <c r="Y7" s="18" t="n">
         <v>63.1308289</v>
       </c>
-      <c r="Z7" s="16" t="n">
+      <c r="Z7" s="18" t="n">
         <v>65.034645</v>
       </c>
-      <c r="AA7" s="16" t="n">
+      <c r="AA7" s="18" t="n">
         <v>70.251322</v>
       </c>
-      <c r="AB7" s="16" t="n">
+      <c r="AB7" s="18" t="n">
         <v>73.60111551600001</v>
       </c>
-      <c r="AC7" s="16" t="n">
+      <c r="AC7" s="18" t="n">
         <v>80.12001189999999</v>
       </c>
-      <c r="AD7" s="16" t="n">
+      <c r="AD7" s="18" t="n">
         <v>83.5619828</v>
       </c>
-      <c r="AE7" s="16" t="n">
+      <c r="AE7" s="18" t="n">
         <v>85.49143599999999</v>
       </c>
-      <c r="AF7" s="16" t="n">
+      <c r="AF7" s="18" t="n">
         <v>88.85136</v>
       </c>
-      <c r="AG7" s="16" t="n">
+      <c r="AG7" s="18" t="n">
         <v>86.97</v>
       </c>
-      <c r="AH7" s="16" t="n">
+      <c r="AH7" s="18" t="n">
         <v>88.42</v>
       </c>
-      <c r="AI7" s="16" t="n">
+      <c r="AI7" s="18" t="n">
         <v>86.92</v>
       </c>
-      <c r="AJ7" s="16" t="n">
+      <c r="AJ7" s="18" t="n">
         <v>88.44</v>
       </c>
-      <c r="AK7" s="16" t="n">
+      <c r="AK7" s="18" t="n">
         <v>83.40000000000001</v>
       </c>
-      <c r="AL7" s="16" t="n">
+      <c r="AL7" s="18" t="n">
         <v>91</v>
       </c>
-      <c r="AM7" s="16" t="n">
+      <c r="AM7" s="18" t="n">
         <v>94.5</v>
       </c>
-      <c r="AN7" s="16" t="n">
+      <c r="AN7" s="18" t="n">
         <v>97.40000000000001</v>
       </c>
-      <c r="AO7" s="16" t="n">
+      <c r="AO7" s="18" t="n">
         <v>102.88</v>
       </c>
-      <c r="AP7" s="16" t="n">
+      <c r="AP7" s="18" t="n">
         <v>102.3</v>
       </c>
-      <c r="AQ7" s="16" t="n">
+      <c r="AQ7" s="18" t="n">
         <v>102.3</v>
       </c>
-      <c r="AR7" s="16" t="n">
+      <c r="AR7" s="18" t="n">
         <v>104.71</v>
       </c>
-      <c r="AS7" s="16" t="n">
+      <c r="AS7" s="18" t="n">
         <v>109.24</v>
       </c>
-      <c r="AT7" s="16" t="n">
+      <c r="AT7" s="18" t="n">
         <v>111</v>
       </c>
-      <c r="AU7" s="16" t="n">
+      <c r="AU7" s="18" t="n">
         <v>115</v>
       </c>
-      <c r="AV7" s="16" t="n">
+      <c r="AV7" s="18" t="n">
         <v>113</v>
       </c>
-      <c r="AW7" s="16" t="n">
+      <c r="AW7" s="18" t="n">
         <v>112</v>
       </c>
-      <c r="AX7" s="16" t="n">
+      <c r="AX7" s="18" t="n">
         <v>106</v>
       </c>
-      <c r="AY7" s="16" t="n">
+      <c r="AY7" s="18" t="n">
         <v>112</v>
       </c>
-      <c r="AZ7" s="16" t="n">
+      <c r="AZ7" s="18" t="n">
         <v>114</v>
       </c>
-      <c r="BA7" s="16" t="n">
+      <c r="BA7" s="18" t="n">
         <v>115</v>
       </c>
     </row>
@@ -2470,106 +2472,106 @@
           <t>Target Value of Goals</t>
         </is>
       </c>
-      <c r="B12" s="16" t="n"/>
-      <c r="C12" s="16" t="n">
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n">
         <v>109.1679131</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="18" t="n">
         <v>142.5756586</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="18" t="n">
         <v>214.5860382</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="18" t="n">
         <v>359.2105393</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="18" t="n">
         <v>456.6056031</v>
       </c>
-      <c r="H12" s="16" t="n">
+      <c r="H12" s="18" t="n">
         <v>527.6668704</v>
       </c>
-      <c r="I12" s="16" t="n">
+      <c r="I12" s="18" t="n">
         <v>603.8541595</v>
       </c>
-      <c r="J12" s="16" t="n">
+      <c r="J12" s="18" t="n">
         <v>661.7449233</v>
       </c>
-      <c r="K12" s="16" t="n">
+      <c r="K12" s="18" t="n">
         <v>798.918289</v>
       </c>
-      <c r="L12" s="16" t="n">
+      <c r="L12" s="18" t="n">
         <v>872.8437361</v>
       </c>
-      <c r="M12" s="16" t="n">
+      <c r="M12" s="18" t="n">
         <v>907.54114</v>
       </c>
-      <c r="N12" s="16" t="n">
+      <c r="N12" s="18" t="n">
         <v>969.0741121999999</v>
       </c>
-      <c r="O12" s="16" t="n">
+      <c r="O12" s="18" t="n">
         <v>1004.791582</v>
       </c>
-      <c r="P12" s="16" t="n">
+      <c r="P12" s="18" t="n">
         <v>1031.6806546</v>
       </c>
-      <c r="Q12" s="16" t="n">
+      <c r="Q12" s="18" t="n">
         <v>1080.5009168</v>
       </c>
-      <c r="R12" s="16" t="n">
+      <c r="R12" s="18" t="n">
         <v>1130.0163686</v>
       </c>
-      <c r="S12" s="16" t="n">
+      <c r="S12" s="18" t="n">
         <v>1154.187533</v>
       </c>
-      <c r="T12" s="16" t="n">
+      <c r="T12" s="18" t="n">
         <v>1178.5892471</v>
       </c>
-      <c r="U12" s="16" t="n">
+      <c r="U12" s="18" t="n">
         <v>1202.2600433</v>
       </c>
-      <c r="V12" s="16" t="n">
+      <c r="V12" s="18" t="n">
         <v>1221.9228014</v>
       </c>
-      <c r="W12" s="16" t="n">
+      <c r="W12" s="18" t="n">
         <v>1247.632843</v>
       </c>
-      <c r="X12" s="16" t="n">
+      <c r="X12" s="18" t="n">
         <v>1265.6921765</v>
       </c>
-      <c r="Y12" s="16" t="n">
+      <c r="Y12" s="18" t="n">
         <v>1286.2883083</v>
       </c>
-      <c r="Z12" s="16" t="n">
+      <c r="Z12" s="18" t="n">
         <v>1300.7068308</v>
       </c>
-      <c r="AA12" s="16" t="n"/>
-      <c r="AB12" s="16" t="n"/>
-      <c r="AC12" s="16" t="n"/>
-      <c r="AD12" s="16" t="n"/>
-      <c r="AE12" s="16" t="n"/>
-      <c r="AF12" s="16" t="n"/>
-      <c r="AG12" s="16" t="n"/>
-      <c r="AH12" s="16" t="n"/>
-      <c r="AI12" s="16" t="n"/>
-      <c r="AJ12" s="16" t="n"/>
-      <c r="AK12" s="16" t="n"/>
-      <c r="AL12" s="16" t="n"/>
-      <c r="AM12" s="16" t="n"/>
-      <c r="AN12" s="16" t="n"/>
-      <c r="AO12" s="16" t="n"/>
-      <c r="AP12" s="16" t="n"/>
-      <c r="AQ12" s="16" t="n"/>
-      <c r="AR12" s="16" t="n"/>
-      <c r="AS12" s="16" t="n"/>
-      <c r="AT12" s="16" t="n"/>
-      <c r="AU12" s="16" t="n"/>
-      <c r="AV12" s="16" t="n"/>
-      <c r="AW12" s="16" t="n"/>
-      <c r="AX12" s="16" t="n"/>
-      <c r="AY12" s="16" t="n"/>
-      <c r="AZ12" s="16" t="n"/>
-      <c r="BA12" s="16" t="n"/>
+      <c r="AA12" s="18" t="n"/>
+      <c r="AB12" s="18" t="n"/>
+      <c r="AC12" s="18" t="n"/>
+      <c r="AD12" s="18" t="n"/>
+      <c r="AE12" s="18" t="n"/>
+      <c r="AF12" s="18" t="n"/>
+      <c r="AG12" s="18" t="n"/>
+      <c r="AH12" s="18" t="n"/>
+      <c r="AI12" s="18" t="n"/>
+      <c r="AJ12" s="18" t="n"/>
+      <c r="AK12" s="18" t="n"/>
+      <c r="AL12" s="18" t="n"/>
+      <c r="AM12" s="18" t="n"/>
+      <c r="AN12" s="18" t="n"/>
+      <c r="AO12" s="18" t="n"/>
+      <c r="AP12" s="18" t="n"/>
+      <c r="AQ12" s="18" t="n"/>
+      <c r="AR12" s="18" t="n"/>
+      <c r="AS12" s="18" t="n"/>
+      <c r="AT12" s="18" t="n"/>
+      <c r="AU12" s="18" t="n"/>
+      <c r="AV12" s="18" t="n"/>
+      <c r="AW12" s="18" t="n"/>
+      <c r="AX12" s="18" t="n"/>
+      <c r="AY12" s="18" t="n"/>
+      <c r="AZ12" s="18" t="n"/>
+      <c r="BA12" s="18" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
